--- a/data/trans_camb/P2A_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,56; 25,64</t>
+          <t>9,58; 26,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,54; 22,29</t>
+          <t>4,95; 22,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,89; 30,26</t>
+          <t>13,07; 29,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,1; 33,91</t>
+          <t>18,39; 35,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,43; 24,16</t>
+          <t>8,39; 25,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,14; 25,95</t>
+          <t>11,42; 26,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,55; 28,39</t>
+          <t>15,99; 28,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,15; 21,68</t>
+          <t>8,78; 20,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,83; 26,79</t>
+          <t>14,13; 25,75</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,6; 67,78</t>
+          <t>19,76; 67,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,6; 57,31</t>
+          <t>10,38; 57,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,35; 78,2</t>
+          <t>28,38; 78,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31,46; 71,98</t>
+          <t>32,02; 76,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,71; 51,25</t>
+          <t>14,18; 54,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,91; 55,74</t>
+          <t>19,66; 57,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,77; 64,32</t>
+          <t>31,56; 63,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,85; 49,85</t>
+          <t>17,67; 47,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>29,4; 60,81</t>
+          <t>27,25; 58,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 12,5</t>
+          <t>0,19; 13,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,8; 16,57</t>
+          <t>4,86; 16,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 0,93</t>
+          <t>-13,98; 0,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 10,62</t>
+          <t>-1,46; 10,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,01; 11,63</t>
+          <t>-0,6; 11,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,07; -13,88</t>
+          <t>-25,74; -14,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 10,03</t>
+          <t>0,74; 9,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 12,56</t>
+          <t>3,77; 12,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-18,16; -9,08</t>
+          <t>-17,8; -8,19</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 28,56</t>
+          <t>0,4; 30,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,65; 38,79</t>
+          <t>9,5; 39,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,91; 2,41</t>
+          <t>-28,14; 0,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 17,2</t>
+          <t>-2,09; 17,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 18,18</t>
+          <t>-0,8; 17,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,99; -22,33</t>
+          <t>-37,98; -22,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 18,7</t>
+          <t>1,2; 18,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,28; 23,17</t>
+          <t>6,63; 22,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-31,46; -16,79</t>
+          <t>-30,52; -15,42</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,9; 22,28</t>
+          <t>7,21; 22,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 15,57</t>
+          <t>0,52; 16,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 11,53</t>
+          <t>-3,45; 11,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 7,87</t>
+          <t>-6,91; 8,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,4; 0,44</t>
+          <t>-13,51; 0,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,78; -9,92</t>
+          <t>-23,92; -9,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 12,56</t>
+          <t>1,99; 12,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 6,51</t>
+          <t>-4,71; 5,93</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,04; -1,83</t>
+          <t>-12,17; -1,75</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,38; 54,31</t>
+          <t>14,64; 55,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,68; 38,14</t>
+          <t>1,06; 40,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 29,03</t>
+          <t>-7,13; 27,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 12,23</t>
+          <t>-9,54; 12,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-20,03; 0,79</t>
+          <t>-19,07; 0,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,19; -15,41</t>
+          <t>-33,45; -15,35</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,62; 22,82</t>
+          <t>3,28; 23,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 12,05</t>
+          <t>-7,93; 11,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-20,35; -3,5</t>
+          <t>-20,55; -3,17</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 14,69</t>
+          <t>-0,03; 14,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 13,48</t>
+          <t>-0,43; 13,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-15,36; 2,36</t>
+          <t>-16,49; 1,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 8,32</t>
+          <t>-4,93; 8,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 7,84</t>
+          <t>-4,55; 8,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-47,56; -17,46</t>
+          <t>-43,5; -17,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 9,31</t>
+          <t>-0,69; 9,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 8,8</t>
+          <t>-0,78; 9,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-29,85; -11,23</t>
+          <t>-30,27; -11,14</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 30,12</t>
+          <t>0,11; 30,28</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 27,77</t>
+          <t>-0,87; 27,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,52; 4,37</t>
+          <t>-30,0; 2,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 12,6</t>
+          <t>-6,78; 12,54</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 11,8</t>
+          <t>-6,32; 12,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,49; -25,71</t>
+          <t>-64,1; -25,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 15,98</t>
+          <t>-1,1; 16,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 15,46</t>
+          <t>-1,22; 15,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-48,75; -19,15</t>
+          <t>-48,1; -18,95</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 16,08</t>
+          <t>-4,06; 16,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 13,37</t>
+          <t>-7,33; 11,66</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-44,17; -28,15</t>
+          <t>-45,8; -28,99</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,14; 24,86</t>
+          <t>7,86; 24,54</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 7,24</t>
+          <t>-10,63; 7,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-60,05; -42,86</t>
+          <t>-60,06; -42,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,91; 18,34</t>
+          <t>5,31; 18,5</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 7,32</t>
+          <t>-5,63; 7,58</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-50,36; -38,08</t>
+          <t>-50,64; -38,37</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 35,46</t>
+          <t>-7,55; 36,63</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 30,42</t>
+          <t>-14,14; 26,52</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-81,35; -63,58</t>
+          <t>-81,66; -63,48</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11,55; 42,04</t>
+          <t>11,18; 41,01</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-15,73; 12,23</t>
+          <t>-15,21; 12,96</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-87,83; -69,98</t>
+          <t>-87,71; -69,92</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,57; 33,85</t>
+          <t>8,67; 34,9</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 13,65</t>
+          <t>-9,34; 13,82</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-83,3; -69,58</t>
+          <t>-83,22; -69,91</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3,71; 20,91</t>
+          <t>3,04; 19,65</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 7,32</t>
+          <t>-10,14; 7,46</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 14,8</t>
+          <t>-1,67; 15,03</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,17; 20,21</t>
+          <t>5,24; 20,59</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 5,1</t>
+          <t>-10,03; 6,58</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-14,98; -0,17</t>
+          <t>-14,79; 0,24</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,68; 18,01</t>
+          <t>6,69; 17,94</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 4,17</t>
+          <t>-7,97; 3,49</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 5,08</t>
+          <t>-5,36; 5,48</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6,49; 44,89</t>
+          <t>5,52; 42,71</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-18,06; 15,94</t>
+          <t>-18,62; 16,03</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 32,38</t>
+          <t>-2,96; 32,1</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7,61; 33,8</t>
+          <t>7,64; 34,77</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-15,66; 8,51</t>
+          <t>-14,76; 11,18</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-21,8; -0,25</t>
+          <t>-21,66; 0,47</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,77; 32,49</t>
+          <t>11,04; 32,97</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-12,77; 7,44</t>
+          <t>-13,08; 6,29</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 9,1</t>
+          <t>-8,99; 10,22</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>6,03; 17,44</t>
+          <t>5,97; 17,53</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 5,19</t>
+          <t>-6,63; 4,61</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-18,39; -6,43</t>
+          <t>-17,99; -7,03</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,7; 12,7</t>
+          <t>2,51; 12,83</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-10,02; 0,8</t>
+          <t>-9,98; 0,85</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-23,99; 16,49</t>
+          <t>-24,28; 15,73</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,99; 13,6</t>
+          <t>5,84; 13,8</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,12; 1,3</t>
+          <t>-6,97; 0,91</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 14,03</t>
+          <t>-18,96; 12,33</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>12,1; 41,05</t>
+          <t>12,47; 40,59</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-14,62; 12,19</t>
+          <t>-13,68; 10,72</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-38,09; -14,85</t>
+          <t>-37,6; -16,1</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2,71; 21,72</t>
+          <t>3,75; 22,1</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-15,96; 1,33</t>
+          <t>-15,67; 1,46</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-38,7; 29,03</t>
+          <t>-38,82; 26,7</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,84; 26,38</t>
+          <t>10,51; 26,69</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 2,49</t>
+          <t>-12,65; 1,76</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-33,98; 27,46</t>
+          <t>-35,14; 23,0</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 1,36</t>
+          <t>-8,89; 1,19</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 5,34</t>
+          <t>-5,31; 4,85</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-41,91; -16,25</t>
+          <t>-42,07; -15,66</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 0,38</t>
+          <t>-9,57; 0,33</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 2,79</t>
+          <t>-6,54; 2,84</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-22,82; -13,47</t>
+          <t>-22,99; -13,4</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-7,74; -0,37</t>
+          <t>-7,53; -0,34</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 2,65</t>
+          <t>-4,44; 2,49</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-36,38; -16,62</t>
+          <t>-38,08; -16,97</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-17,0; 2,93</t>
+          <t>-16,71; 2,55</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-9,36; 11,23</t>
+          <t>-9,96; 9,89</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-78,78; -32,28</t>
+          <t>-79,42; -31,96</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-14,44; 0,62</t>
+          <t>-14,41; 0,56</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 4,62</t>
+          <t>-10,03; 4,72</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-35,16; -22,1</t>
+          <t>-34,94; -22,43</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-13,1; -0,64</t>
+          <t>-12,73; -0,62</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 4,73</t>
+          <t>-7,57; 4,48</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-63,85; -29,5</t>
+          <t>-65,36; -29,91</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>5,26; 10,26</t>
+          <t>4,98; 9,73</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,55; 6,72</t>
+          <t>1,53; 6,45</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-17,65; -5,95</t>
+          <t>-19,03; -6,18</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3,25; 7,79</t>
+          <t>3,28; 7,81</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 2,12</t>
+          <t>-2,29; 2,26</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-19,91; -6,66</t>
+          <t>-20,14; -5,94</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,83; 8,23</t>
+          <t>4,75; 8,25</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,71</t>
+          <t>0,3; 3,68</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-16,75; -7,64</t>
+          <t>-16,89; -8,09</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>10,68; 21,92</t>
+          <t>10,07; 20,69</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3,11; 14,7</t>
+          <t>3,1; 13,71</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-36,69; -12,61</t>
+          <t>-39,72; -13,03</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5,0; 12,48</t>
+          <t>5,04; 12,39</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 3,37</t>
+          <t>-3,54; 3,61</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-31,03; -10,23</t>
+          <t>-31,28; -9,37</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>8,45; 14,83</t>
+          <t>8,27; 14,88</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0,41; 6,73</t>
+          <t>0,54; 6,71</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-29,91; -13,73</t>
+          <t>-30,06; -14,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21,57</t>
+          <t>16,89</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,44</t>
+          <t>14,59</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>20,0</t>
+          <t>15,83</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,58; 26,17</t>
+          <t>9,82; 25,97</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,95; 22,13</t>
+          <t>4,44; 21,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,07; 29,76</t>
+          <t>8,52; 25,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,39; 35,17</t>
+          <t>17,57; 33,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,39; 25,43</t>
+          <t>7,92; 24,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,42; 26,39</t>
+          <t>6,92; 21,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,99; 28,11</t>
+          <t>16,13; 27,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,78; 20,92</t>
+          <t>8,88; 21,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>14,13; 25,75</t>
+          <t>9,96; 21,61</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>39,2%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>33,3%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,76; 67,88</t>
+          <t>20,71; 67,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,38; 57,09</t>
+          <t>9,5; 57,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,38; 78,28</t>
+          <t>17,52; 65,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32,02; 76,25</t>
+          <t>30,98; 72,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,18; 54,18</t>
+          <t>13,62; 52,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,66; 57,36</t>
+          <t>11,98; 47,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,56; 63,4</t>
+          <t>31,81; 62,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,67; 47,42</t>
+          <t>17,6; 48,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>27,25; 58,8</t>
+          <t>19,36; 49,16</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-6,43</t>
+          <t>-7,04</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-19,93</t>
+          <t>-20,43</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-13,29</t>
+          <t>-13,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 13,19</t>
+          <t>-0,3; 12,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,86; 16,93</t>
+          <t>4,25; 17,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,98; 0,1</t>
+          <t>-14,5; -0,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 10,71</t>
+          <t>-1,08; 10,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 11,08</t>
+          <t>-0,67; 11,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-25,74; -14,32</t>
+          <t>-26,25; -14,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 9,92</t>
+          <t>0,91; 10,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 12,27</t>
+          <t>3,66; 12,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-17,8; -8,19</t>
+          <t>-18,27; -9,48</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-13,74%</t>
+          <t>-15,05%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-30,41%</t>
+          <t>-31,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-23,62%</t>
+          <t>-24,53%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 30,71</t>
+          <t>-0,58; 28,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,5; 39,68</t>
+          <t>8,23; 39,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,14; 0,07</t>
+          <t>-28,87; -1,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 17,37</t>
+          <t>-1,53; 16,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 17,87</t>
+          <t>-0,93; 17,64</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,98; -22,64</t>
+          <t>-38,56; -23,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 18,07</t>
+          <t>1,5; 18,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,63; 22,84</t>
+          <t>6,18; 23,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-30,52; -15,42</t>
+          <t>-31,43; -17,54</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,12</t>
+          <t>3,61</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-16,99</t>
+          <t>-17,26</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-6,68</t>
+          <t>-7,05</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,21; 22,74</t>
+          <t>7,59; 22,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 16,15</t>
+          <t>0,38; 15,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 11,36</t>
+          <t>-3,94; 10,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 8,09</t>
+          <t>-7,21; 7,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 0,05</t>
+          <t>-13,34; 1,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,92; -9,78</t>
+          <t>-24,32; -10,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,99; 12,57</t>
+          <t>2,33; 13,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 5,93</t>
+          <t>-4,68; 6,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,17; -1,75</t>
+          <t>-12,38; -1,91</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-24,96%</t>
+          <t>-25,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-11,78%</t>
+          <t>-12,44%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>14,64; 55,39</t>
+          <t>15,73; 57,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,06; 40,18</t>
+          <t>0,7; 38,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 27,58</t>
+          <t>-7,73; 26,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,54; 12,84</t>
+          <t>-10,11; 11,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-19,07; 0,1</t>
+          <t>-18,47; 2,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,45; -15,35</t>
+          <t>-33,75; -16,27</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,28; 23,47</t>
+          <t>3,93; 24,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 11,09</t>
+          <t>-7,92; 11,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-20,55; -3,17</t>
+          <t>-20,59; -3,22</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-7,15</t>
+          <t>-7,42</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-28,82</t>
+          <t>-18,2</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-18,56</t>
+          <t>-12,75</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 14,44</t>
+          <t>-0,18; 14,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 13,34</t>
+          <t>-1,03; 13,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,49; 1,13</t>
+          <t>-15,72; 0,98</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 8,45</t>
+          <t>-4,7; 8,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 8,38</t>
+          <t>-4,52; 8,01</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-43,5; -17,4</t>
+          <t>-24,45; -11,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 9,29</t>
+          <t>-0,54; 9,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 9,03</t>
+          <t>-0,62; 9,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-30,27; -11,14</t>
+          <t>-17,82; -7,18</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-13,79%</t>
+          <t>-14,3%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-41,44%</t>
+          <t>-26,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-30,49%</t>
+          <t>-20,95%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,11; 30,28</t>
+          <t>-0,32; 30,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 27,9</t>
+          <t>-2,57; 28,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-30,0; 2,28</t>
+          <t>-28,94; 1,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 12,54</t>
+          <t>-6,42; 12,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 12,45</t>
+          <t>-6,15; 12,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-64,1; -25,28</t>
+          <t>-34,13; -17,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 16,02</t>
+          <t>-0,81; 16,64</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 15,41</t>
+          <t>-0,98; 16,33</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-48,1; -18,95</t>
+          <t>-28,67; -12,63</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-36,79</t>
+          <t>-37,5</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-50,96</t>
+          <t>-47,87</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-43,79</t>
+          <t>-42,62</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 16,26</t>
+          <t>-3,18; 16,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,33; 11,66</t>
+          <t>-7,2; 13,23</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-45,8; -28,99</t>
+          <t>-45,68; -29,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,86; 24,54</t>
+          <t>7,41; 24,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 7,66</t>
+          <t>-10,33; 7,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-60,06; -42,98</t>
+          <t>-55,54; -40,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,31; 18,5</t>
+          <t>4,55; 18,45</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 7,58</t>
+          <t>-5,97; 7,66</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-50,64; -38,37</t>
+          <t>-48,23; -36,31</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-73,85%</t>
+          <t>-75,29%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-77,33%</t>
+          <t>-72,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-75,57%</t>
+          <t>-73,56%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 36,63</t>
+          <t>-5,81; 35,93</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 26,52</t>
+          <t>-12,7; 30,08</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-81,66; -63,48</t>
+          <t>-82,52; -66,41</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>11,18; 41,01</t>
+          <t>10,66; 40,6</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 12,96</t>
+          <t>-14,57; 12,01</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-87,71; -69,92</t>
+          <t>-78,32; -66,38</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,67; 34,9</t>
+          <t>7,42; 34,09</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 13,82</t>
+          <t>-9,79; 13,68</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-83,22; -69,91</t>
+          <t>-77,9; -67,74</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6,65</t>
+          <t>6,52</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-7,08</t>
+          <t>-7,72</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>-0,69</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3,04; 19,65</t>
+          <t>3,16; 20,09</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 7,46</t>
+          <t>-9,71; 7,12</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 15,03</t>
+          <t>-1,94; 14,93</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,24; 20,59</t>
+          <t>4,31; 20,32</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 6,58</t>
+          <t>-12,41; 5,3</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 0,24</t>
+          <t>-15,07; 0,46</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,69; 17,94</t>
+          <t>6,52; 18,11</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 3,49</t>
+          <t>-7,36; 4,33</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 5,48</t>
+          <t>-6,65; 4,73</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-10,97%</t>
+          <t>-11,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-0,53%</t>
+          <t>-1,19%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5,52; 42,71</t>
+          <t>5,68; 42,57</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-18,62; 16,03</t>
+          <t>-17,77; 15,6</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 32,1</t>
+          <t>-3,39; 32,16</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7,64; 34,77</t>
+          <t>6,39; 33,91</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-14,76; 11,18</t>
+          <t>-17,87; 8,95</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-21,66; 0,47</t>
+          <t>-22,26; 0,71</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>11,04; 32,97</t>
+          <t>10,72; 33,4</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 6,29</t>
+          <t>-12,09; 7,98</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 10,22</t>
+          <t>-10,87; 8,62</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-12,54</t>
+          <t>-12,73</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-7,58</t>
+          <t>-21,14</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-8,62</t>
+          <t>-16,95</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5,97; 17,53</t>
+          <t>6,83; 18,27</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,63; 4,61</t>
+          <t>-6,29; 5,16</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-17,99; -7,03</t>
+          <t>-18,26; -6,79</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,51; 12,83</t>
+          <t>2,08; 12,53</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 0,85</t>
+          <t>-10,69; 0,47</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-24,28; 15,73</t>
+          <t>-26,33; -16,37</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,84; 13,8</t>
+          <t>5,67; 13,6</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 0,91</t>
+          <t>-6,96; 1,28</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-18,96; 12,33</t>
+          <t>-21,1; -13,03</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-27,47%</t>
+          <t>-27,9%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-12,35%</t>
+          <t>-34,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-16,07%</t>
+          <t>-31,6%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>12,47; 40,59</t>
+          <t>13,84; 42,26</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 10,72</t>
+          <t>-12,96; 11,82</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-37,6; -16,1</t>
+          <t>-37,54; -15,7</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3,75; 22,1</t>
+          <t>3,25; 21,56</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-15,67; 1,46</t>
+          <t>-16,46; 0,79</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-38,82; 26,7</t>
+          <t>-40,96; -27,81</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,51; 26,69</t>
+          <t>10,01; 26,56</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 1,76</t>
+          <t>-12,55; 2,46</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-35,14; 23,0</t>
+          <t>-37,73; -25,09</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-26,57</t>
+          <t>-18,68</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-18,14</t>
+          <t>-18,58</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-23,82</t>
+          <t>-18,66</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 1,19</t>
+          <t>-9,64; 1,27</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 4,85</t>
+          <t>-5,63; 5,19</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-42,07; -15,66</t>
+          <t>-23,86; -13,98</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-9,57; 0,33</t>
+          <t>-9,22; 0,28</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 2,84</t>
+          <t>-7,19; 2,52</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-22,99; -13,4</t>
+          <t>-23,09; -13,77</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-7,53; -0,34</t>
+          <t>-8,21; -0,79</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 2,49</t>
+          <t>-4,62; 2,54</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-38,08; -16,97</t>
+          <t>-21,94; -15,21</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-51,83%</t>
+          <t>-36,44%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-28,67%</t>
+          <t>-29,37%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-41,48%</t>
+          <t>-32,5%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-16,71; 2,55</t>
+          <t>-17,56; 2,51</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 9,89</t>
+          <t>-10,38; 10,65</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-79,42; -31,96</t>
+          <t>-44,23; -28,76</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-14,41; 0,56</t>
+          <t>-14,04; 0,44</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 4,72</t>
+          <t>-11,03; 4,14</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-34,94; -22,43</t>
+          <t>-35,31; -22,85</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-12,73; -0,62</t>
+          <t>-13,9; -1,43</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 4,48</t>
+          <t>-7,96; 4,51</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-65,36; -29,91</t>
+          <t>-37,27; -27,37</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-10,03</t>
+          <t>-8,58</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-15,92</t>
+          <t>-17,57</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-12,92</t>
+          <t>-13,1</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>4,98; 9,73</t>
+          <t>5,07; 9,89</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1,53; 6,45</t>
+          <t>1,38; 6,46</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-19,03; -6,18</t>
+          <t>-11,21; -6,27</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3,28; 7,81</t>
+          <t>3,14; 7,82</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 2,26</t>
+          <t>-2,34; 2,34</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-20,14; -5,94</t>
+          <t>-19,68; -15,47</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>4,75; 8,25</t>
+          <t>4,62; 8,06</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,68</t>
+          <t>0,32; 3,68</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-16,89; -8,09</t>
+          <t>-14,76; -11,23</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-20,84%</t>
+          <t>-17,82%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-24,93%</t>
+          <t>-27,53%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-23,03%</t>
+          <t>-23,35%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>10,07; 20,69</t>
+          <t>10,08; 21,02</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>3,1; 13,71</t>
+          <t>2,89; 13,8</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-39,72; -13,03</t>
+          <t>-22,63; -13,1</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>5,04; 12,39</t>
+          <t>4,75; 12,4</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 3,61</t>
+          <t>-3,62; 3,72</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-31,28; -9,37</t>
+          <t>-30,25; -24,72</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>8,27; 14,88</t>
+          <t>8,08; 14,57</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0,54; 6,71</t>
+          <t>0,62; 6,67</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-30,06; -14,5</t>
+          <t>-25,85; -20,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_R-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares que tienen personas con alguna condición, enfermedad crónica o limitación</t>
+          <t>Población que convive con personas con alguna condición, enfermedad crónica o limitación</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
